--- a/examples/HFP_dana.xlsx
+++ b/examples/HFP_dana.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,6 +476,11 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>QCD</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>big-ticket items</t>
         </is>
       </c>
@@ -517,6 +522,9 @@
       <c r="L2" t="n">
         <v>0</v>
       </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -555,6 +563,9 @@
       <c r="L3" t="n">
         <v>0</v>
       </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -593,6 +604,9 @@
       <c r="L4" t="n">
         <v>0</v>
       </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -631,6 +645,9 @@
       <c r="L5" t="n">
         <v>0</v>
       </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -669,6 +686,9 @@
       <c r="L6" t="n">
         <v>0</v>
       </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -707,6 +727,9 @@
       <c r="L7" t="n">
         <v>0</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -745,6 +768,9 @@
       <c r="L8" t="n">
         <v>0</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -783,6 +809,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -821,6 +850,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -859,6 +891,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -897,6 +932,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -935,6 +973,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -973,6 +1014,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1011,6 +1055,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1049,6 +1096,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1087,6 +1137,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1125,6 +1178,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1163,6 +1219,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1201,6 +1260,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1239,6 +1301,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1277,6 +1342,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1315,6 +1383,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1353,6 +1424,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1391,6 +1465,9 @@
       <c r="L25" t="n">
         <v>0</v>
       </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1429,6 +1506,9 @@
       <c r="L26" t="n">
         <v>0</v>
       </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1467,6 +1547,9 @@
       <c r="L27" t="n">
         <v>0</v>
       </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1503,6 +1586,9 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
         <v>0</v>
       </c>
     </row>

--- a/examples/HFP_dana.xlsx
+++ b/examples/HFP_dana.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:N28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,10 +476,15 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>Roth conv fixed</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>QCD</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>big-ticket items</t>
         </is>
@@ -519,10 +524,10 @@
       <c r="K2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
       <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -560,10 +565,10 @@
       <c r="K3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
       <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -601,10 +606,10 @@
       <c r="K4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
       <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -642,10 +647,10 @@
       <c r="K5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
       <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -683,10 +688,10 @@
       <c r="K6" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
       <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -724,10 +729,10 @@
       <c r="K7" t="n">
         <v>0</v>
       </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
       <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -765,10 +770,10 @@
       <c r="K8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
       <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -806,10 +811,10 @@
       <c r="K9" t="n">
         <v>0</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
       <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -847,10 +852,10 @@
       <c r="K10" t="n">
         <v>0</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
       <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -888,10 +893,10 @@
       <c r="K11" t="n">
         <v>0</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
       <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -929,10 +934,10 @@
       <c r="K12" t="n">
         <v>0</v>
       </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
       <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -970,10 +975,10 @@
       <c r="K13" t="n">
         <v>0</v>
       </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
       <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1011,10 +1016,10 @@
       <c r="K14" t="n">
         <v>0</v>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1052,10 +1057,10 @@
       <c r="K15" t="n">
         <v>0</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
       <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1093,10 +1098,10 @@
       <c r="K16" t="n">
         <v>0</v>
       </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
       <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1134,10 +1139,10 @@
       <c r="K17" t="n">
         <v>0</v>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
       <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1175,10 +1180,10 @@
       <c r="K18" t="n">
         <v>0</v>
       </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
       <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1216,10 +1221,10 @@
       <c r="K19" t="n">
         <v>0</v>
       </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
       <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1257,10 +1262,10 @@
       <c r="K20" t="n">
         <v>0</v>
       </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
       <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1298,10 +1303,10 @@
       <c r="K21" t="n">
         <v>0</v>
       </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
       <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1339,10 +1344,10 @@
       <c r="K22" t="n">
         <v>0</v>
       </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
       <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1380,10 +1385,10 @@
       <c r="K23" t="n">
         <v>0</v>
       </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
       <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1421,10 +1426,10 @@
       <c r="K24" t="n">
         <v>0</v>
       </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1462,10 +1467,10 @@
       <c r="K25" t="n">
         <v>0</v>
       </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
       <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1503,10 +1508,10 @@
       <c r="K26" t="n">
         <v>0</v>
       </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
       <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1544,10 +1549,10 @@
       <c r="K27" t="n">
         <v>0</v>
       </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
       <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1585,10 +1590,10 @@
       <c r="K28" t="n">
         <v>0</v>
       </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
       <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
         <v>0</v>
       </c>
     </row>
